--- a/data/pack/uk/defra_sheep_output_index.xlsx
+++ b/data/pack/uk/defra_sheep_output_index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K152"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8794,6 +8794,61 @@
         </is>
       </c>
       <c r="K152" t="inlineStr">
+        <is>
+          <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: Defra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>defra_sheep_output_index</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Índice de precios percibidos: Ovino (Defra)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>152.45</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>index_2020_100</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>INDEX</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>UK Defra (gov.uk agricultural statistics)</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>OGL-UK-3.0</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>Contains public sector information licensed under the Open Government Licence v3.0. Source: Defra.</t>
         </is>
@@ -8893,7 +8948,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -8904,7 +8959,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
@@ -8999,7 +9054,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
